--- a/excel/PayGuard_Regression_Evaluation.xlsx
+++ b/excel/PayGuard_Regression_Evaluation.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>flydubai  |  PayGuard AI</t>
+          <t>PayGuard AI</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>flydubai  |  PayGuard AI</t>
+          <t>PayGuard AI</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>flydubai  |  PayGuard AI</t>
+          <t>PayGuard AI</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>flydubai  |  PayGuard AI</t>
+          <t>PayGuard AI</t>
         </is>
       </c>
     </row>
